--- a/TalentMaster_Pelaajarekisteri.xlsx
+++ b/TalentMaster_Pelaajarekisteri.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,6 +97,9 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -218,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -287,6 +290,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -712,7 +716,7 @@
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>PalloID</t>
+          <t>PalloID (vapaaehtoinen)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -753,7 +757,7 @@
       <c r="E8" s="21" t="n"/>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t>3.  PalloID löytyy pelipassista tai MyWay-palvelusta.</t>
+          <t>3.  PalloID löytyy pelipassista tai Palloliiton rekisteristä.</t>
         </is>
       </c>
     </row>
@@ -765,7 +769,7 @@
       <c r="E9" s="21" t="n"/>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>4.  Huoltajan s-posti: kutsu lähtee sinne automaattisesti.</t>
+          <t>4.  Huoltajan s-posti: vanhempi saa tätä kautta suostumuspyynnön.</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1485,107 +1489,115 @@
           <t>Seuran joukkueet</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>← TalentMaster kirjoittaa joukkueet automaattisesti tänne latauksen yhteydessä.</t>
-        </is>
-      </c>
+      <c r="B1" s="14" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="15" t="inlineStr"/>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Lisää seurasi joukkueet alla olevaan listaan — yksi joukkue per rivi.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="16" t="inlineStr"/>
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Nämä näkyvät Joukkue-sarakkeen valintaluettelossa Pelaajat-välilehdellä.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="15" t="inlineStr"/>
+      <c r="A4" s="15" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="16" t="inlineStr"/>
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>Joukkue</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr"/>
+      <c r="A6" s="15" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="16" t="inlineStr"/>
+      <c r="A7" s="16" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr"/>
+      <c r="A8" s="15" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="16" t="inlineStr"/>
+      <c r="A9" s="16" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr"/>
+      <c r="A10" s="15" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="16" t="inlineStr"/>
+      <c r="A11" s="16" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr"/>
+      <c r="A12" s="15" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="16" t="inlineStr"/>
+      <c r="A13" s="16" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="15" t="inlineStr"/>
+      <c r="A14" s="15" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="16" t="inlineStr"/>
+      <c r="A15" s="16" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="15" t="inlineStr"/>
+      <c r="A16" s="15" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="16" t="inlineStr"/>
+      <c r="A17" s="16" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="15" t="inlineStr"/>
+      <c r="A18" s="15" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="16" t="inlineStr"/>
+      <c r="A19" s="16" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="15" t="inlineStr"/>
+      <c r="A20" s="15" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="16" t="inlineStr"/>
+      <c r="A21" s="16" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="15" t="inlineStr"/>
+      <c r="A22" s="15" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="16" t="inlineStr"/>
+      <c r="A23" s="16" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="15" t="inlineStr"/>
+      <c r="A24" s="15" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="16" t="inlineStr"/>
+      <c r="A25" s="16" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="15" t="inlineStr"/>
+      <c r="A26" s="15" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="16" t="inlineStr"/>
+      <c r="A27" s="16" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="15" t="inlineStr"/>
+      <c r="A28" s="15" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="16" t="inlineStr"/>
+      <c r="A29" s="16" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="15" t="inlineStr"/>
-    </row>
+      <c r="A30" s="15" t="n"/>
+    </row>
+    <row r="31"/>
     <row r="32" ht="48" customHeight="1">
-      <c r="A32" s="17" t="inlineStr">
-        <is>
-          <t>ℹ️  Tämä välilehti täytetään automaattisesti kun lataat pohjan TalentMaster-järjestelmästä. Jos lataat pohjan suoraan GitHubista ilman järjestelmää, kirjoita seuran joukkueet käsin riveille 2–30.</t>
-        </is>
-      </c>
+      <c r="A32" s="17" t="n"/>
       <c r="B32" s="5" t="n"/>
     </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A32:B32"/>
@@ -1676,6 +1688,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="17" t="inlineStr">
         <is>

--- a/TalentMaster_Pelaajarekisteri.xlsx
+++ b/TalentMaster_Pelaajarekisteri.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -100,6 +100,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -221,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -291,6 +295,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -656,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -664,7 +669,8 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -719,7 +725,17 @@
           <t>PalloID</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>Talenttiohjelma</t>
+        </is>
+      </c>
+      <c r="G5" s="31" t="inlineStr">
+        <is>
+          <t>TalenttiTaso</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>📋  OHJE SIHTEEREILLE</t>
         </is>
@@ -731,7 +747,7 @@
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="9" t="n"/>
       <c r="E6" s="21" t="n"/>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>1.  Täytä jokainen pelaaja omalle rivilleen.</t>
         </is>
@@ -743,7 +759,7 @@
       <c r="C7" s="11" t="n"/>
       <c r="D7" s="12" t="n"/>
       <c r="E7" s="21" t="n"/>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>2.  Joukkue: valitse dropdownista ▼</t>
         </is>
@@ -755,7 +771,7 @@
       <c r="C8" s="8" t="n"/>
       <c r="D8" s="9" t="n"/>
       <c r="E8" s="21" t="n"/>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>3.  PalloID (vapaaehtoinen) — löytyy pelipassista tai Palloliiton rekisteristä.</t>
         </is>
@@ -767,9 +783,9 @@
       <c r="C9" s="11" t="n"/>
       <c r="D9" s="12" t="n"/>
       <c r="E9" s="21" t="n"/>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>4.  Huoltajan s-posti: vanhempi saa tätä kautta suostumuspyynnön.</t>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>4.  Talenttiohjelma: kirjoita "kyllä" jos pelaaja on talenttiryhmässä.</t>
         </is>
       </c>
     </row>
@@ -779,9 +795,9 @@
       <c r="C10" s="8" t="n"/>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="21" t="n"/>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>5.  Tallenna → lataa takaisin TalentMasteriin.</t>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>5.  TalenttiTaso: "perus" tai "laajennettu" (jätä tyhjäksi jos ei talentti).</t>
         </is>
       </c>
     </row>
@@ -791,9 +807,9 @@
       <c r="C11" s="11" t="n"/>
       <c r="D11" s="12" t="n"/>
       <c r="E11" s="21" t="n"/>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>6.  Vanhempi täyttää loput suostumuslomakkeessa.</t>
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t>6.  Huoltajan s-posti: vanhempi saa tätä kautta suostumuspyynnön.</t>
         </is>
       </c>
     </row>
@@ -803,6 +819,11 @@
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="21" t="n"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>7.  Tallenna → lataa takaisin TalentMasteriin.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="11" t="n"/>
@@ -1461,9 +1482,15 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="3">
     <dataValidation sqref="C6:C105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Tuntematon joukkue" error="Valitse joukkue listasta (Asetukset-välilehti)." type="list">
       <formula1>=Asetukset!$A$2:$A$30</formula1>
+    </dataValidation>
+    <dataValidation sqref="F6:F105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kyllä,ei"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G6:G105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"perus,laajennettu"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
